--- a/test_files/report_lviv_2026-09-30.xlsx
+++ b/test_files/report_lviv_2026-09-30.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,7 +470,6 @@
           <t>Widget A</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
